--- a/Assets/StreamingAssets/Localization/English.xlsx
+++ b/Assets/StreamingAssets/Localization/English.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\nbcamp\AirNHook\Assets\StreamingAssets\Localization\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Unity\AirNHook\Assets\StreamingAssets\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B3254FF-531E-40F2-A66E-43262E705194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29524789-1A11-4090-ACE5-2C9DD63BA8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22410" yWindow="3645" windowWidth="21600" windowHeight="11385" xr2:uid="{03AB7020-0D5B-4C42-B659-F913FE2E7807}"/>
+    <workbookView xWindow="4335" yWindow="1200" windowWidth="22785" windowHeight="13485" xr2:uid="{03AB7020-0D5B-4C42-B659-F913FE2E7807}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>id</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -142,11 +142,19 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>This option is not available in menu</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>FullScreen</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Map Editor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>This option is not available now</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Start Stage</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -587,7 +595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D177C49-BEC9-445E-96B9-01949D401546}">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="51.5" customWidth="1"/>
@@ -654,7 +662,7 @@
         <v>1006</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="17.25" thickBot="1">
@@ -718,7 +726,7 @@
         <v>1014</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="17.25" thickBot="1">
@@ -795,17 +803,33 @@
     </row>
     <row r="26" spans="1:2" ht="17.25" thickBot="1">
       <c r="A26" s="1">
-        <v>4001</v>
+        <v>2010</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="17.25" thickBot="1">
       <c r="A27" s="1">
+        <v>2101</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="17.25" thickBot="1">
+      <c r="A28" s="1">
+        <v>4001</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="17.25" thickBot="1">
+      <c r="A29" s="1">
         <v>4002</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B29" s="2" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Localization/English.xlsx
+++ b/Assets/StreamingAssets/Localization/English.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Unity\AirNHook\Assets\StreamingAssets\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29524789-1A11-4090-ACE5-2C9DD63BA8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA24053-DC96-4E2B-9380-0EED417F262A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4335" yWindow="1200" windowWidth="22785" windowHeight="13485" xr2:uid="{03AB7020-0D5B-4C42-B659-F913FE2E7807}"/>
+    <workbookView xWindow="4680" yWindow="1545" windowWidth="22785" windowHeight="13485" xr2:uid="{03AB7020-0D5B-4C42-B659-F913FE2E7807}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>id</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -155,6 +155,10 @@
   </si>
   <si>
     <t>Start Stage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sorry, Current UserTestBuild does not contain SOUNDS yet!!!</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -595,7 +599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D177C49-BEC9-445E-96B9-01949D401546}">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="51.5" customWidth="1"/>
@@ -729,107 +733,115 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="17.25" thickBot="1">
+    <row r="17" spans="1:2" ht="28.5" thickBot="1">
       <c r="A17" s="1">
-        <v>2001</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
+        <v>1015</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="17.25" thickBot="1">
       <c r="A18" s="1">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="17.25" thickBot="1">
       <c r="A19" s="1">
-        <v>2003</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>10</v>
+        <v>2002</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="17.25" thickBot="1">
       <c r="A20" s="1">
-        <v>2004</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>11</v>
+        <v>2003</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="17.25" thickBot="1">
       <c r="A21" s="1">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="17.25" thickBot="1">
       <c r="A22" s="1">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="17.25" thickBot="1">
       <c r="A23" s="1">
-        <v>2007</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>5</v>
+        <v>2006</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="17.25" thickBot="1">
       <c r="A24" s="1">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="17.25" thickBot="1">
       <c r="A25" s="1">
-        <v>2009</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>7</v>
+        <v>2008</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="17.25" thickBot="1">
       <c r="A26" s="1">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="17.25" thickBot="1">
       <c r="A27" s="1">
-        <v>2101</v>
+        <v>2010</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="17.25" thickBot="1">
       <c r="A28" s="1">
-        <v>4001</v>
+        <v>2101</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="17.25" thickBot="1">
       <c r="A29" s="1">
+        <v>4001</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="17.25" thickBot="1">
+      <c r="A30" s="1">
         <v>4002</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B30" s="2" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Localization/English.xlsx
+++ b/Assets/StreamingAssets/Localization/English.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Unity\AirNHook\Assets\StreamingAssets\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA24053-DC96-4E2B-9380-0EED417F262A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0190486C-78CA-4BF7-A51E-8F84E9F7AC81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="1545" windowWidth="22785" windowHeight="13485" xr2:uid="{03AB7020-0D5B-4C42-B659-F913FE2E7807}"/>
+    <workbookView xWindow="2550" yWindow="1140" windowWidth="22785" windowHeight="13485" xr2:uid="{03AB7020-0D5B-4C42-B659-F913FE2E7807}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>id</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -160,6 +160,9 @@
   <si>
     <t>Sorry, Current UserTestBuild does not contain SOUNDS yet!!!</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Disabled when in game</t>
   </si>
 </sst>
 </file>
@@ -599,7 +602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D177C49-BEC9-445E-96B9-01949D401546}">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="51.5" customWidth="1"/>
@@ -743,105 +746,113 @@
     </row>
     <row r="18" spans="1:2" ht="17.25" thickBot="1">
       <c r="A18" s="1">
-        <v>2001</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
+        <v>1016</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="17.25" thickBot="1">
       <c r="A19" s="1">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="17.25" thickBot="1">
       <c r="A20" s="1">
-        <v>2003</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>10</v>
+        <v>2002</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="17.25" thickBot="1">
       <c r="A21" s="1">
-        <v>2004</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>11</v>
+        <v>2003</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="17.25" thickBot="1">
       <c r="A22" s="1">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="17.25" thickBot="1">
       <c r="A23" s="1">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="17.25" thickBot="1">
       <c r="A24" s="1">
-        <v>2007</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>5</v>
+        <v>2006</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="17.25" thickBot="1">
       <c r="A25" s="1">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="17.25" thickBot="1">
       <c r="A26" s="1">
-        <v>2009</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>7</v>
+        <v>2008</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="17.25" thickBot="1">
       <c r="A27" s="1">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="17.25" thickBot="1">
       <c r="A28" s="1">
-        <v>2101</v>
+        <v>2010</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="17.25" thickBot="1">
       <c r="A29" s="1">
-        <v>4001</v>
+        <v>2101</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="17.25" thickBot="1">
       <c r="A30" s="1">
+        <v>4001</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="17.25" thickBot="1">
+      <c r="A31" s="1">
         <v>4002</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B31" s="2" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Localization/English.xlsx
+++ b/Assets/StreamingAssets/Localization/English.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Unity\AirNHook\Assets\StreamingAssets\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0190486C-78CA-4BF7-A51E-8F84E9F7AC81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE4B1C53-F871-4D02-830D-E15CCAA1D0FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2550" yWindow="1140" windowWidth="22785" windowHeight="13485" xr2:uid="{03AB7020-0D5B-4C42-B659-F913FE2E7807}"/>
+    <workbookView xWindow="3240" yWindow="1830" windowWidth="22785" windowHeight="13485" xr2:uid="{03AB7020-0D5B-4C42-B659-F913FE2E7807}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>id</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -163,6 +163,10 @@
   </si>
   <si>
     <t>Disabled when in game</t>
+  </si>
+  <si>
+    <t>Join Code</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -602,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D177C49-BEC9-445E-96B9-01949D401546}">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="51.5" customWidth="1"/>
@@ -754,105 +758,113 @@
     </row>
     <row r="19" spans="1:2" ht="17.25" thickBot="1">
       <c r="A19" s="1">
-        <v>2001</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
+        <v>1017</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="17.25" thickBot="1">
       <c r="A20" s="1">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="17.25" thickBot="1">
       <c r="A21" s="1">
-        <v>2003</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>10</v>
+        <v>2002</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="17.25" thickBot="1">
       <c r="A22" s="1">
-        <v>2004</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>11</v>
+        <v>2003</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="17.25" thickBot="1">
       <c r="A23" s="1">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="17.25" thickBot="1">
       <c r="A24" s="1">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="17.25" thickBot="1">
       <c r="A25" s="1">
-        <v>2007</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>5</v>
+        <v>2006</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="17.25" thickBot="1">
       <c r="A26" s="1">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="17.25" thickBot="1">
       <c r="A27" s="1">
-        <v>2009</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>7</v>
+        <v>2008</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="17.25" thickBot="1">
       <c r="A28" s="1">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="17.25" thickBot="1">
       <c r="A29" s="1">
-        <v>2101</v>
+        <v>2010</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="17.25" thickBot="1">
       <c r="A30" s="1">
-        <v>4001</v>
+        <v>2101</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="17.25" thickBot="1">
       <c r="A31" s="1">
+        <v>4001</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="17.25" thickBot="1">
+      <c r="A32" s="1">
         <v>4002</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B32" s="2" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Localization/English.xlsx
+++ b/Assets/StreamingAssets/Localization/English.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <x:si>
     <x:t>Now, this is the first REAL obstacle of your life, not like that stupid puberty.</x:t>
   </x:si>
@@ -27,121 +27,124 @@
     <x:t>Sorry, Current UserTestBuild does not contain SOUNDS yet!!!</x:t>
   </x:si>
   <x:si>
+    <x:t>You can use your hook to swing to the next platform!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Where you become useful beans and do your solemn duty!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Just do as I say and follow the crash course.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>This is the first tutorial course so if you are smarter than squirrels. There would be no problem!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>If your dumb partner is dead, We will slide another one of the clones through the pipe right away.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Air</x:t>
+  </x:si>
+  <x:si>
+    <x:t>id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StageRestart</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENTER ROOM CODE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>APPLY CHANGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Press ESC to Exit</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Failed to Connect</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Welcome to SUPER SOLDIER TRAINING LAB!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Option</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hook</x:t>
+  </x:si>
+  <x:si>
+    <x:t>text</x:t>
+  </x:si>
+  <x:si>
+    <x:t>English</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lobby</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Effects</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Master</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Exit</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RETRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vsync</x:t>
+  </x:si>
+  <x:si>
+    <x:t>But remember both of you need to cross. So use your airgun creatively.</x:t>
+  </x:si>
+  <x:si>
     <x:t>This is the second tutorial course. It seems you two were smarter than average beans.</x:t>
   </x:si>
   <x:si>
-    <x:t>Just do as I say and follow the crash course.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>If your dumb partner is dead, We will slide another one of the clones through the pipe right away.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>This is the first tutorial course so if you are smarter than squirrels. There would be no problem!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Where you become useful beans and do your solemn duty!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>You can use your hook to swing to the next platform!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Press ESC to Exit</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Failed to Connect</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Welcome to SUPER SOLDIER TRAINING LAB!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Option</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JOIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hook</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lobby</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Master</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RETRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Vsync</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Exit</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Effects</x:t>
-  </x:si>
-  <x:si>
-    <x:t>text</x:t>
-  </x:si>
-  <x:si>
-    <x:t>English</x:t>
-  </x:si>
-  <x:si>
-    <x:t>But remember both of you need to cross. So use your airgun creatively.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StageRestart</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENTER ROOM CODE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>APPLY CHANGE</x:t>
+    <x:t>Disabled when in game</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Stage Start</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Create Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FullScreen</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Enter Code</x:t>
   </x:si>
   <x:si>
     <x:t>ExitGame</x:t>
   </x:si>
   <x:si>
-    <x:t>Enter Code</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Create Room</x:t>
+    <x:t>Map Editor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Language</x:t>
   </x:si>
   <x:si>
     <x:t>Join Game</x:t>
   </x:si>
   <x:si>
+    <x:t>Join Code</x:t>
+  </x:si>
+  <x:si>
     <x:t>Resolution</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FullScreen</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map Editor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Language</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Join Code</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Start Stage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Disabled when in game</x:t>
-  </x:si>
-  <x:si>
-    <x:t>id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Air</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BGM</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -766,7 +769,7 @@
       </x:fill>
     </x:dxf>
   </x:dxfs>
-  <x:tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+  <x:tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <x:tableStyle name="PivotStyleLight16" pivot="1" table="0" count="11">
       <x:tableStyleElement type="headerRow" size="1" dxfId="0"/>
       <x:tableStyleElement type="totalRow" size="1" dxfId="1"/>
@@ -1105,7 +1108,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:B42"/>
+  <x:dimension ref="A1:B43"/>
   <x:sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.399999999999999"/>
   <x:cols>
     <x:col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
@@ -1114,10 +1117,10 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" t="s">
-        <x:v>40</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B1" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
@@ -1125,7 +1128,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="B2" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -1133,7 +1136,7 @@
         <x:v>1001</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
@@ -1141,7 +1144,7 @@
         <x:v>1002</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
@@ -1149,7 +1152,7 @@
         <x:v>1003</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
@@ -1157,7 +1160,7 @@
         <x:v>1004</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
@@ -1165,7 +1168,7 @@
         <x:v>1005</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
@@ -1173,7 +1176,7 @@
         <x:v>1006</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
@@ -1181,7 +1184,7 @@
         <x:v>1007</x:v>
       </x:c>
       <x:c r="B9" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2">
@@ -1189,7 +1192,7 @@
         <x:v>1008</x:v>
       </x:c>
       <x:c r="B10" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
@@ -1197,7 +1200,7 @@
         <x:v>1009</x:v>
       </x:c>
       <x:c r="B11" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:2">
@@ -1205,7 +1208,7 @@
         <x:v>1010</x:v>
       </x:c>
       <x:c r="B12" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
@@ -1213,7 +1216,7 @@
         <x:v>1011</x:v>
       </x:c>
       <x:c r="B13" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
@@ -1221,7 +1224,7 @@
         <x:v>1012</x:v>
       </x:c>
       <x:c r="B14" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
@@ -1229,7 +1232,7 @@
         <x:v>1013</x:v>
       </x:c>
       <x:c r="B15" s="5" t="s">
-        <x:v>28</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:2">
@@ -1240,7 +1243,7 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:2" ht="27.399999999999999">
+    <x:row r="17" spans="1:2">
       <x:c r="A17" s="1">
         <x:v>1015</x:v>
       </x:c>
@@ -1253,7 +1256,7 @@
         <x:v>1016</x:v>
       </x:c>
       <x:c r="B18" s="5" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:2">
@@ -1261,7 +1264,7 @@
         <x:v>1017</x:v>
       </x:c>
       <x:c r="B19" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:2">
@@ -1269,7 +1272,7 @@
         <x:v>2001</x:v>
       </x:c>
       <x:c r="B20" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:2">
@@ -1277,7 +1280,7 @@
         <x:v>2002</x:v>
       </x:c>
       <x:c r="B21" s="3" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:2">
@@ -1285,7 +1288,7 @@
         <x:v>2003</x:v>
       </x:c>
       <x:c r="B22" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:2" ht="17.149999999999999">
@@ -1293,7 +1296,7 @@
         <x:v>2004</x:v>
       </x:c>
       <x:c r="B23" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:2" ht="17.149999999999999">
@@ -1301,7 +1304,7 @@
         <x:v>2005</x:v>
       </x:c>
       <x:c r="B24" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:2" ht="17.149999999999999">
@@ -1309,7 +1312,7 @@
         <x:v>2006</x:v>
       </x:c>
       <x:c r="B25" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:2">
@@ -1317,7 +1320,7 @@
         <x:v>2007</x:v>
       </x:c>
       <x:c r="B26" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:2">
@@ -1325,7 +1328,7 @@
         <x:v>2008</x:v>
       </x:c>
       <x:c r="B27" s="3" t="s">
-        <x:v>30</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:2">
@@ -1333,7 +1336,7 @@
         <x:v>2009</x:v>
       </x:c>
       <x:c r="B28" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:2">
@@ -1341,52 +1344,52 @@
         <x:v>2010</x:v>
       </x:c>
       <x:c r="B29" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:2">
       <x:c r="A30" s="1">
-        <x:v>2101</x:v>
+        <x:v>2011</x:v>
       </x:c>
       <x:c r="B30" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:2">
       <x:c r="A31" s="1">
-        <x:v>4001</x:v>
+        <x:v>2101</x:v>
       </x:c>
       <x:c r="B31" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:2">
       <x:c r="A32" s="1">
+        <x:v>4001</x:v>
+      </x:c>
+      <x:c r="B32" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:2">
+      <x:c r="A33" s="1">
         <x:v>4002</x:v>
       </x:c>
-      <x:c r="B32" s="2" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:2">
-      <x:c r="A33">
-        <x:v>10001</x:v>
-      </x:c>
-      <x:c r="B33" t="s">
-        <x:v>12</x:v>
+      <x:c r="B33" s="2" t="s">
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:2">
       <x:c r="A34">
-        <x:v>10002</x:v>
+        <x:v>10001</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:2">
       <x:c r="A35">
-        <x:v>10003</x:v>
+        <x:v>10002</x:v>
       </x:c>
       <x:c r="B35" t="s">
         <x:v>5</x:v>
@@ -1394,62 +1397,70 @@
     </x:row>
     <x:row r="36" spans="1:2">
       <x:c r="A36">
-        <x:v>10004</x:v>
+        <x:v>10003</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:2">
       <x:c r="A37">
-        <x:v>10005</x:v>
+        <x:v>10004</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>0</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:2">
       <x:c r="A38">
-        <x:v>10006</x:v>
+        <x:v>10005</x:v>
       </x:c>
       <x:c r="B38" t="s">
-        <x:v>9</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:2">
       <x:c r="A39">
-        <x:v>10007</x:v>
+        <x:v>10006</x:v>
       </x:c>
       <x:c r="B39" t="s">
-        <x:v>25</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:2">
       <x:c r="A40">
-        <x:v>10008</x:v>
+        <x:v>10007</x:v>
       </x:c>
       <x:c r="B40" t="s">
-        <x:v>1</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:2">
       <x:c r="A41">
-        <x:v>10009</x:v>
+        <x:v>10008</x:v>
       </x:c>
       <x:c r="B41" t="s">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:2">
       <x:c r="A42">
+        <x:v>10009</x:v>
+      </x:c>
+      <x:c r="B42" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:2">
+      <x:c r="A43">
         <x:v>10010</x:v>
       </x:c>
-      <x:c r="B42" t="s">
-        <x:v>4</x:v>
+      <x:c r="B43" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
--- a/Assets/StreamingAssets/Localization/English.xlsx
+++ b/Assets/StreamingAssets/Localization/English.xlsx
@@ -3,7 +3,7 @@
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:fileVersion appName="HCell" lastEdited="9.0" lowestEdited="9.0" rupBuild="0.568"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="28365" windowHeight="8280"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="14985" windowHeight="9030"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="Sheet1" sheetId="1" r:id="rId4"/>
@@ -13,138 +13,162 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+  <x:si>
+    <x:t>Good, If you activate the bean pipe, consider that as a checkpoint for the course.</x:t>
+  </x:si>
   <x:si>
     <x:t>Now, this is the first REAL obstacle of your life, not like that stupid puberty.</x:t>
   </x:si>
   <x:si>
-    <x:t>Good, If you activate the bean pipe, consider that as a checkpoint for the course.</x:t>
-  </x:si>
-  <x:si>
     <x:t>This option is not available now</x:t>
   </x:si>
   <x:si>
+    <x:t>You can use your hook to swing to the next platform!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Where you become useful beans and do your solemn duty!</x:t>
+  </x:si>
+  <x:si>
     <x:t>Sorry, Current UserTestBuild does not contain SOUNDS yet!!!</x:t>
   </x:si>
   <x:si>
-    <x:t>You can use your hook to swing to the next platform!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Where you become useful beans and do your solemn duty!</x:t>
+    <x:t>I hope you succeed this time, unlike the ones before you.</x:t>
   </x:si>
   <x:si>
     <x:t>Just do as I say and follow the crash course.</x:t>
   </x:si>
   <x:si>
+    <x:t>If your dumb partner is dead, We will slide another one of the clones through the pipe right away.</x:t>
+  </x:si>
+  <x:si>
     <x:t>This is the first tutorial course so if you are smarter than squirrels. There would be no problem!</x:t>
   </x:si>
   <x:si>
-    <x:t>If your dumb partner is dead, We will slide another one of the clones through the pipe right away.</x:t>
+    <x:t>id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Air</x:t>
   </x:si>
   <x:si>
     <x:t>BGM</x:t>
   </x:si>
   <x:si>
-    <x:t>Air</x:t>
-  </x:si>
-  <x:si>
-    <x:t>id</x:t>
+    <x:t>ENTER ROOM CODE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>APPLY CHANGE</x:t>
   </x:si>
   <x:si>
     <x:t>StageRestart</x:t>
   </x:si>
   <x:si>
-    <x:t>ENTER ROOM CODE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>APPLY CHANGE</x:t>
+    <x:t>Alright, now that you've learned all the basics, it's time to start the final test course.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Welcome to SUPER SOLDIER TRAINING LAB!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Failed to Connect</x:t>
   </x:si>
   <x:si>
     <x:t>Press ESC to Exit</x:t>
   </x:si>
   <x:si>
-    <x:t>Failed to Connect</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Welcome to SUPER SOLDIER TRAINING LAB!</x:t>
+    <x:t>RETRY</x:t>
   </x:si>
   <x:si>
     <x:t>Option</x:t>
   </x:si>
   <x:si>
+    <x:t>JOIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Exit</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Effects</x:t>
+  </x:si>
+  <x:si>
     <x:t>Hook</x:t>
   </x:si>
   <x:si>
+    <x:t>English</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Master</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lobby</x:t>
+  </x:si>
+  <x:si>
     <x:t>text</x:t>
   </x:si>
   <x:si>
-    <x:t>English</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JOIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lobby</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Effects</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Master</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Exit</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RETRY</x:t>
-  </x:si>
-  <x:si>
     <x:t>Vsync</x:t>
   </x:si>
   <x:si>
+    <x:t>Enter Code</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ExitGame</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Stage Start</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Create Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map Editor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FullScreen</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Language</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Join Game</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Resolution</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Join Code</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Well done.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Disabled when in game</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ah, they died. What number was it again…? Oh right, [/1st]!</x:t>
+  </x:si>
+  <x:si>
     <x:t>But remember both of you need to cross. So use your airgun creatively.</x:t>
   </x:si>
   <x:si>
+    <x:t>They sure do die a lot! That one is on their [/1st] reproduction now.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Took you long enough. But at least you made it through the course, so that’s something.</x:t>
+  </x:si>
+  <x:si>
     <x:t>This is the second tutorial course. It seems you two were smarter than average beans.</x:t>
   </x:si>
   <x:si>
-    <x:t>Disabled when in game</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Stage Start</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Create Room</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loading...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FullScreen</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Enter Code</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ExitGame</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map Editor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Language</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Join Game</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Join Code</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Resolution</x:t>
+    <x:t>What, dead again? I expected a lot of deaths, but this is already their [/1st] time.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[Horrifying!] But worry not! With the cutting-edge technology of our super lab, we can reproduce as many times as needed!</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -283,7 +307,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="7">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -311,6 +335,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1108,7 +1135,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:B43"/>
+  <x:dimension ref="A1:B51"/>
   <x:sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.399999999999999"/>
   <x:cols>
     <x:col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
@@ -1117,10 +1144,10 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B1" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
@@ -1128,7 +1155,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="B2" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -1136,7 +1163,7 @@
         <x:v>1001</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
@@ -1144,7 +1171,7 @@
         <x:v>1002</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
@@ -1152,7 +1179,7 @@
         <x:v>1003</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
@@ -1160,7 +1187,7 @@
         <x:v>1004</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
@@ -1168,7 +1195,7 @@
         <x:v>1005</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
@@ -1176,7 +1203,7 @@
         <x:v>1006</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
@@ -1184,7 +1211,7 @@
         <x:v>1007</x:v>
       </x:c>
       <x:c r="B9" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2">
@@ -1192,7 +1219,7 @@
         <x:v>1008</x:v>
       </x:c>
       <x:c r="B10" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
@@ -1200,7 +1227,7 @@
         <x:v>1009</x:v>
       </x:c>
       <x:c r="B11" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:2">
@@ -1208,7 +1235,7 @@
         <x:v>1010</x:v>
       </x:c>
       <x:c r="B12" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
@@ -1216,7 +1243,7 @@
         <x:v>1011</x:v>
       </x:c>
       <x:c r="B13" s="5" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
@@ -1224,7 +1251,7 @@
         <x:v>1012</x:v>
       </x:c>
       <x:c r="B14" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
@@ -1248,7 +1275,7 @@
         <x:v>1015</x:v>
       </x:c>
       <x:c r="B17" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:2">
@@ -1256,7 +1283,7 @@
         <x:v>1016</x:v>
       </x:c>
       <x:c r="B18" s="5" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:2">
@@ -1272,7 +1299,7 @@
         <x:v>2001</x:v>
       </x:c>
       <x:c r="B20" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:2">
@@ -1280,7 +1307,7 @@
         <x:v>2002</x:v>
       </x:c>
       <x:c r="B21" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:2">
@@ -1288,7 +1315,7 @@
         <x:v>2003</x:v>
       </x:c>
       <x:c r="B22" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:2" ht="17.149999999999999">
@@ -1296,7 +1323,7 @@
         <x:v>2004</x:v>
       </x:c>
       <x:c r="B23" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:2" ht="17.149999999999999">
@@ -1304,7 +1331,7 @@
         <x:v>2005</x:v>
       </x:c>
       <x:c r="B24" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:2" ht="17.149999999999999">
@@ -1312,7 +1339,7 @@
         <x:v>2006</x:v>
       </x:c>
       <x:c r="B25" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:2">
@@ -1328,7 +1355,7 @@
         <x:v>2008</x:v>
       </x:c>
       <x:c r="B27" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:2">
@@ -1344,7 +1371,7 @@
         <x:v>2010</x:v>
       </x:c>
       <x:c r="B29" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:2">
@@ -1352,7 +1379,7 @@
         <x:v>2011</x:v>
       </x:c>
       <x:c r="B30" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:2">
@@ -1360,7 +1387,7 @@
         <x:v>2101</x:v>
       </x:c>
       <x:c r="B31" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:2">
@@ -1368,7 +1395,7 @@
         <x:v>4001</x:v>
       </x:c>
       <x:c r="B32" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:2">
@@ -1376,7 +1403,7 @@
         <x:v>4002</x:v>
       </x:c>
       <x:c r="B33" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:2">
@@ -1392,7 +1419,7 @@
         <x:v>10002</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:2">
@@ -1400,7 +1427,7 @@
         <x:v>10003</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:2">
@@ -1408,7 +1435,7 @@
         <x:v>10004</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:2">
@@ -1416,7 +1443,7 @@
         <x:v>10005</x:v>
       </x:c>
       <x:c r="B38" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:2">
@@ -1424,7 +1451,7 @@
         <x:v>10006</x:v>
       </x:c>
       <x:c r="B39" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:2">
@@ -1432,7 +1459,7 @@
         <x:v>10007</x:v>
       </x:c>
       <x:c r="B40" t="s">
-        <x:v>30</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:2">
@@ -1440,7 +1467,7 @@
         <x:v>10008</x:v>
       </x:c>
       <x:c r="B41" t="s">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:2">
@@ -1456,7 +1483,71 @@
         <x:v>10010</x:v>
       </x:c>
       <x:c r="B43" t="s">
-        <x:v>31</x:v>
+        <x:v>49</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:2">
+      <x:c r="A44">
+        <x:v>50000</x:v>
+      </x:c>
+      <x:c r="B44" s="6" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:2">
+      <x:c r="A45">
+        <x:v>50001</x:v>
+      </x:c>
+      <x:c r="B45" s="6" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:2">
+      <x:c r="A46">
+        <x:v>50002</x:v>
+      </x:c>
+      <x:c r="B46" s="6" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:2">
+      <x:c r="A47">
+        <x:v>50003</x:v>
+      </x:c>
+      <x:c r="B47" s="6" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:2">
+      <x:c r="A48">
+        <x:v>70001</x:v>
+      </x:c>
+      <x:c r="B48" s="6" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:2">
+      <x:c r="A49">
+        <x:v>70010</x:v>
+      </x:c>
+      <x:c r="B49" s="6" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:2">
+      <x:c r="A50">
+        <x:v>70011</x:v>
+      </x:c>
+      <x:c r="B50" s="6" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:2">
+      <x:c r="A51">
+        <x:v>70012</x:v>
+      </x:c>
+      <x:c r="B51" s="6" t="s">
+        <x:v>45</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Assets/StreamingAssets/Localization/English.xlsx
+++ b/Assets/StreamingAssets/Localization/English.xlsx
@@ -15,160 +15,160 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <x:si>
+    <x:t>But remember both of you need to cross. So use your airgun creatively.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They sure do die a lot! That one is on their [/1st] reproduction now.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Well done. You did bring the key, right?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Air</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>This is the first tutorial course so if you are smarter than squirrels. There would be no problem!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>If your dumb partner is dead, We will slide another one of the clones through the pipe right away.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Welcome to SUPER SOLDIER TRAINING LAB!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vsync</x:t>
+  </x:si>
+  <x:si>
+    <x:t>text</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Alright, now that you've learned all the basics, it's time to start the final test course.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ah, they died. What number was it again…? Oh right, [/1st]!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sorry, Current UserTestBuild does not contain SOUNDS yet!!!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>I hope you succeed this time, unlike the ones before you.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[Horrifying!] But worry not! With the cutting-edge technology of our super lab, we can reproduce as many times as needed!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>This option is not available now</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FullScreen</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Resolution</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Language</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Create Room</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Enter Code</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Join Game</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loading...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Map Editor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Join Code</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Stage Start</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ExitGame</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Failed to Connect</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Press ESC to Exit</x:t>
+  </x:si>
+  <x:si>
+    <x:t>APPLY CHANGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StageRestart</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENTER ROOM CODE</x:t>
+  </x:si>
+  <x:si>
     <x:t>Good, If you activate the bean pipe, consider that as a checkpoint for the course.</x:t>
   </x:si>
   <x:si>
     <x:t>Now, this is the first REAL obstacle of your life, not like that stupid puberty.</x:t>
   </x:si>
   <x:si>
-    <x:t>This option is not available now</x:t>
+    <x:t>What, dead again? I expected a lot of deaths, but this is already their [/1st] time.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>This is the second tutorial course. It seems you two were smarter than average beans.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Took you long enough. But at least you made it through the course, so that’s something.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Where you become useful beans and do your solemn duty!</x:t>
   </x:si>
   <x:si>
     <x:t>You can use your hook to swing to the next platform!</x:t>
   </x:si>
   <x:si>
-    <x:t>Where you become useful beans and do your solemn duty!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sorry, Current UserTestBuild does not contain SOUNDS yet!!!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>I hope you succeed this time, unlike the ones before you.</x:t>
-  </x:si>
-  <x:si>
     <x:t>Just do as I say and follow the crash course.</x:t>
   </x:si>
   <x:si>
-    <x:t>If your dumb partner is dead, We will slide another one of the clones through the pipe right away.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>This is the first tutorial course so if you are smarter than squirrels. There would be no problem!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Air</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENTER ROOM CODE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>APPLY CHANGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StageRestart</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Alright, now that you've learned all the basics, it's time to start the final test course.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Welcome to SUPER SOLDIER TRAINING LAB!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Failed to Connect</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Press ESC to Exit</x:t>
-  </x:si>
-  <x:si>
     <x:t>RETRY</x:t>
   </x:si>
   <x:si>
     <x:t>Option</x:t>
   </x:si>
   <x:si>
+    <x:t>Lobby</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Effects</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Master</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hook</x:t>
+  </x:si>
+  <x:si>
+    <x:t>English</x:t>
+  </x:si>
+  <x:si>
     <x:t>JOIN</x:t>
   </x:si>
   <x:si>
     <x:t>Exit</x:t>
   </x:si>
   <x:si>
-    <x:t>Effects</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hook</x:t>
-  </x:si>
-  <x:si>
-    <x:t>English</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Master</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lobby</x:t>
-  </x:si>
-  <x:si>
-    <x:t>text</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Vsync</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Enter Code</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ExitGame</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Stage Start</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Create Room</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Map Editor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FullScreen</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Language</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Join Game</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Resolution</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Loading...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Join Code</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Well done.</x:t>
-  </x:si>
-  <x:si>
     <x:t>Disabled when in game</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ah, they died. What number was it again…? Oh right, [/1st]!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>But remember both of you need to cross. So use your airgun creatively.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They sure do die a lot! That one is on their [/1st] reproduction now.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Took you long enough. But at least you made it through the course, so that’s something.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>This is the second tutorial course. It seems you two were smarter than average beans.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>What, dead again? I expected a lot of deaths, but this is already their [/1st] time.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[Horrifying!] But worry not! With the cutting-edge technology of our super lab, we can reproduce as many times as needed!</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -350,7 +350,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -395,7 +394,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -472,7 +470,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -511,7 +508,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -534,7 +530,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -567,7 +562,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -615,7 +609,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -671,7 +664,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -706,7 +698,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -739,7 +730,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -762,7 +752,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1144,10 +1133,10 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B1" t="s">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="B1" t="s">
-        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
@@ -1155,7 +1144,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="B2" t="s">
-        <x:v>26</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -1163,7 +1152,7 @@
         <x:v>1001</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
@@ -1171,7 +1160,7 @@
         <x:v>1002</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
@@ -1179,7 +1168,7 @@
         <x:v>1003</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>28</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
@@ -1187,7 +1176,7 @@
         <x:v>1004</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
@@ -1195,7 +1184,7 @@
         <x:v>1005</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
@@ -1203,7 +1192,7 @@
         <x:v>1006</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
@@ -1211,7 +1200,7 @@
         <x:v>1007</x:v>
       </x:c>
       <x:c r="B9" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2">
@@ -1219,7 +1208,7 @@
         <x:v>1008</x:v>
       </x:c>
       <x:c r="B10" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
@@ -1227,7 +1216,7 @@
         <x:v>1009</x:v>
       </x:c>
       <x:c r="B11" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:2">
@@ -1235,7 +1224,7 @@
         <x:v>1010</x:v>
       </x:c>
       <x:c r="B12" s="5" t="s">
-        <x:v>38</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
@@ -1243,7 +1232,7 @@
         <x:v>1011</x:v>
       </x:c>
       <x:c r="B13" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
@@ -1251,7 +1240,7 @@
         <x:v>1012</x:v>
       </x:c>
       <x:c r="B14" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
@@ -1259,7 +1248,7 @@
         <x:v>1013</x:v>
       </x:c>
       <x:c r="B15" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:2">
@@ -1267,7 +1256,7 @@
         <x:v>1014</x:v>
       </x:c>
       <x:c r="B16" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:2">
@@ -1275,7 +1264,7 @@
         <x:v>1015</x:v>
       </x:c>
       <x:c r="B17" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:2">
@@ -1283,7 +1272,7 @@
         <x:v>1016</x:v>
       </x:c>
       <x:c r="B18" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:2">
@@ -1291,7 +1280,7 @@
         <x:v>1017</x:v>
       </x:c>
       <x:c r="B19" s="5" t="s">
-        <x:v>42</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:2">
@@ -1299,7 +1288,7 @@
         <x:v>2001</x:v>
       </x:c>
       <x:c r="B20" s="3" t="s">
-        <x:v>39</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:2">
@@ -1307,7 +1296,7 @@
         <x:v>2002</x:v>
       </x:c>
       <x:c r="B21" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:2">
@@ -1315,7 +1304,7 @@
         <x:v>2003</x:v>
       </x:c>
       <x:c r="B22" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:2" ht="17.149999999999999">
@@ -1323,7 +1312,7 @@
         <x:v>2004</x:v>
       </x:c>
       <x:c r="B23" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:2" ht="17.149999999999999">
@@ -1331,7 +1320,7 @@
         <x:v>2005</x:v>
       </x:c>
       <x:c r="B24" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:2" ht="17.149999999999999">
@@ -1339,7 +1328,7 @@
         <x:v>2006</x:v>
       </x:c>
       <x:c r="B25" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:2">
@@ -1347,7 +1336,7 @@
         <x:v>2007</x:v>
       </x:c>
       <x:c r="B26" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:2">
@@ -1355,7 +1344,7 @@
         <x:v>2008</x:v>
       </x:c>
       <x:c r="B27" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:2">
@@ -1363,7 +1352,7 @@
         <x:v>2009</x:v>
       </x:c>
       <x:c r="B28" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:2">
@@ -1371,7 +1360,7 @@
         <x:v>2010</x:v>
       </x:c>
       <x:c r="B29" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:2">
@@ -1379,7 +1368,7 @@
         <x:v>2011</x:v>
       </x:c>
       <x:c r="B30" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:2">
@@ -1387,7 +1376,7 @@
         <x:v>2101</x:v>
       </x:c>
       <x:c r="B31" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:2">
@@ -1395,7 +1384,7 @@
         <x:v>4001</x:v>
       </x:c>
       <x:c r="B32" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:2">
@@ -1403,7 +1392,7 @@
         <x:v>4002</x:v>
       </x:c>
       <x:c r="B33" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:2">
@@ -1411,7 +1400,7 @@
         <x:v>10001</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>17</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:2">
@@ -1419,7 +1408,7 @@
         <x:v>10002</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>4</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:2">
@@ -1427,7 +1416,7 @@
         <x:v>10003</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>7</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:2">
@@ -1435,7 +1424,7 @@
         <x:v>10004</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>9</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:2">
@@ -1443,7 +1432,7 @@
         <x:v>10005</x:v>
       </x:c>
       <x:c r="B38" t="s">
-        <x:v>1</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:2">
@@ -1451,7 +1440,7 @@
         <x:v>10006</x:v>
       </x:c>
       <x:c r="B39" t="s">
-        <x:v>3</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:2">
@@ -1459,7 +1448,7 @@
         <x:v>10007</x:v>
       </x:c>
       <x:c r="B40" t="s">
-        <x:v>46</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:2">
@@ -1467,7 +1456,7 @@
         <x:v>10008</x:v>
       </x:c>
       <x:c r="B41" t="s">
-        <x:v>0</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:2">
@@ -1475,7 +1464,7 @@
         <x:v>10009</x:v>
       </x:c>
       <x:c r="B42" t="s">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:2">
@@ -1483,7 +1472,7 @@
         <x:v>10010</x:v>
       </x:c>
       <x:c r="B43" t="s">
-        <x:v>49</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:2">
@@ -1491,7 +1480,7 @@
         <x:v>50000</x:v>
       </x:c>
       <x:c r="B44" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:2">
@@ -1499,7 +1488,7 @@
         <x:v>50001</x:v>
       </x:c>
       <x:c r="B45" s="6" t="s">
-        <x:v>6</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:2">
@@ -1507,7 +1496,7 @@
         <x:v>50002</x:v>
       </x:c>
       <x:c r="B46" s="6" t="s">
-        <x:v>48</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:2">
@@ -1515,7 +1504,7 @@
         <x:v>50003</x:v>
       </x:c>
       <x:c r="B47" s="6" t="s">
-        <x:v>43</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:2">
@@ -1523,7 +1512,7 @@
         <x:v>70001</x:v>
       </x:c>
       <x:c r="B48" s="6" t="s">
-        <x:v>51</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:2">
@@ -1531,7 +1520,7 @@
         <x:v>70010</x:v>
       </x:c>
       <x:c r="B49" s="6" t="s">
-        <x:v>47</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:2">
@@ -1539,7 +1528,7 @@
         <x:v>70011</x:v>
       </x:c>
       <x:c r="B50" s="6" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:2">
@@ -1547,7 +1536,7 @@
         <x:v>70012</x:v>
       </x:c>
       <x:c r="B51" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
